--- a/consulting_forms/027_invisible_bead_extension_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/027_invisible_bead_extension_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>micro_loop</t>
+          <t>micro loop</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nano_loop</t>
+          <t>nano loop</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nano_silk</t>
+          <t>nano silk</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4_inch</t>
+          <t>4 inch</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6_inch</t>
+          <t>6 inch</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8_inch</t>
+          <t>8 inch</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10_inch</t>
+          <t>10 inch</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>micro_loop</t>
+          <t>micro loop</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nano_loop</t>
+          <t>nano loop</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nano_silk</t>
+          <t>nano silk</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4_inch</t>
+          <t>4 inch</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6_inch</t>
+          <t>6 inch</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8_inch</t>
+          <t>8 inch</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10_inch</t>
+          <t>10 inch</t>
         </is>
       </c>
     </row>
